--- a/common/excel/xls/monster.xlsx
+++ b/common/excel/xls/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Leraning\POELike\common\excel\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A8A7A4-A195-45B1-BF29-6773AC29C982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A2FAC9-4808-4D98-A01D-DF4A53B85CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>convert(monster.txt,MonstDataConf.pb,MonstDataConf)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,13 +55,32 @@
   </si>
   <si>
     <t>TT_HeavySwordman</t>
+  </si>
+  <si>
+    <t>MonsterAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterDefense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterRadius</t>
+  </si>
+  <si>
+    <t>MonsterDetectionRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +94,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFD0D0D0"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,8 +122,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -379,20 +407,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="47.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -402,8 +435,23 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -413,8 +461,23 @@
       <c r="C3">
         <v>10</v>
       </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -424,8 +487,23 @@
       <c r="C4">
         <v>100</v>
       </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3001</v>
       </c>
@@ -435,8 +513,23 @@
       <c r="C5">
         <v>1000</v>
       </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4001</v>
       </c>
@@ -445,6 +538,21 @@
       </c>
       <c r="C6">
         <v>10000</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/common/excel/xls/monster.xlsx
+++ b/common/excel/xls/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Leraning\POELike\common\excel\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A2FAC9-4808-4D98-A01D-DF4A53B85CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728FAFC2-DCCC-45F5-B535-EF8C04AA68F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>convert(monster.txt,MonstDataConf.pb,MonstDataConf)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,6 +73,10 @@
   </si>
   <si>
     <t>MonsterDetectionRange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterBaseExp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="47.75" bestFit="1" customWidth="1"/>
@@ -418,14 +422,15 @@
     <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -450,8 +455,11 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -476,8 +484,11 @@
       <c r="H3">
         <v>10</v>
       </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -502,8 +513,11 @@
       <c r="H4">
         <v>12</v>
       </c>
+      <c r="I4">
+        <v>150</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3001</v>
       </c>
@@ -528,8 +542,11 @@
       <c r="H5">
         <v>14</v>
       </c>
+      <c r="I5">
+        <v>300</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4001</v>
       </c>
@@ -553,6 +570,9 @@
       </c>
       <c r="H6">
         <v>18</v>
+      </c>
+      <c r="I6">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/common/excel/xls/monster.xlsx
+++ b/common/excel/xls/monster.xlsx
@@ -410,8 +410,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="47.75" bestFit="1" customWidth="1"/>
@@ -425,154 +425,346 @@
     <col min="9" max="9" width="14.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>convert(monster.txt,MonstDataConf.pb,MonstDataConf)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
+    <row r="2" spans="1:13">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MonsterID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MonsterMesh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MonsterHp</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MonsterAttack</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MonsterDefense</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MonsterSpeed</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="1">
+        <is>
+          <t>MonsterRadius</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MonsterDetectionRange</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MonsterBaseExp</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="1">
+        <is>
+          <t>MonsterAttackRange</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="1">
+        <is>
+          <t>MonsterAttackDuration</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="1">
+        <is>
+          <t>MonsterAttackInterval</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="1">
+        <is>
+          <t>MonsterSpawnTriggerRadius</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
-        <v>1001</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>100</v>
+    <row r="3" spans="1:13">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TT_Halberdier</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
-        <v>2001</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>80</v>
-      </c>
-      <c r="F4">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>12</v>
-      </c>
-      <c r="I4">
-        <v>150</v>
+    <row r="4" spans="1:13">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TT_Heavy_Cavalry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>3001</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>60</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>14</v>
-      </c>
-      <c r="I5">
-        <v>300</v>
+    <row r="5" spans="1:13">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TT_Heavy_Infantry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
-        <v>4001</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>10000</v>
-      </c>
-      <c r="D6">
-        <v>40</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>600</v>
+    <row r="6" spans="1:13">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TT_HeavySwordman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
     </row>
   </sheetData>
